--- a/reports/pdf_rolling5_20261020.xlsx
+++ b/reports/pdf_rolling5_20261020.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,651억   ·   현금 208억(4.5%)      오늘 2026-10-20  vs  5일전 2026-10-13      매수 16종목  /  매도 25종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,644억      오늘 2026-10-20  vs  5일전 2026-10-13      매수 16종목  /  매도 25종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>489</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4419540829</v>
+        <v>4432923525</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-454</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4089716362</v>
+        <v>-4102100326</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>147</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1362079318</v>
+        <v>1366203795</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-152</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2949373191</v>
+        <v>-2958304111</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>139</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>512426042</v>
+        <v>513977706</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-129</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3432475557</v>
+        <v>-3442869347</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>737957717</v>
+        <v>740192308</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-103</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1808732720</v>
+        <v>-1814209697</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>841556809</v>
+        <v>844105106</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-73</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1801339864</v>
+        <v>-1806794454</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>965927252</v>
+        <v>968852151</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-61</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-855381253</v>
+        <v>-857971411</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1541202485</v>
+        <v>1545869360</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-59</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-3075467972</v>
+        <v>-3084780717</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>31</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1433133985</v>
+        <v>1437473621</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-52</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1991710875</v>
+        <v>-1997741924</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1129838576</v>
+        <v>1133259810</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-35</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-889669837</v>
+        <v>-892363823</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>910480827</v>
+        <v>913237831</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-26</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1411976145</v>
+        <v>-1416251713</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>864151599</v>
+        <v>866768314</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-23</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-947048710</v>
+        <v>-949916444</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1581635266</v>
+        <v>864034813</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.37%→2.09%</t>
+          <t>1.02%→1.18%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>92→111</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>-21</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-822034118</v>
+        <v>-824523299</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>861426350</v>
+        <v>1586424575</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.18%</t>
+          <t>1.37%→2.09%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>92→111</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>-20</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-996945537</v>
+        <v>-999964362</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1379471360</v>
+        <v>1383648501</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-19</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1589166862</v>
+        <v>-1593978977</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1108631185</v>
+        <v>1111988203</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-17</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2700572846</v>
+        <v>-2708750381</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1650014234</v>
+        <v>1655010599</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>-15</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1883394626</v>
+        <v>-1889097684</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-985449943</v>
+        <v>-988433958</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-781799537</v>
+        <v>-463402968</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.11%</t>
+          <t>0.33%→0.27%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-855331703</v>
+        <v>-857921711</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1451,23 +1451,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-462003986</v>
+        <v>-784166884</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.27%</t>
+          <t>1.27%→1.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1942359098</v>
+        <v>-1948240706</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1245686422</v>
+        <v>-1249458453</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>-5</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-440994795</v>
+        <v>-442330160</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-955323557</v>
+        <v>-958216347</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>-4</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-765844445</v>
+        <v>-768163478</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,080억   ·   현금 60억(1.9%)      오늘 2026-10-20  vs  5일전 2026-10-13      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,166억      오늘 2026-10-20  vs  5일전 2026-10-13      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1710,7 +1710,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1531309203</v>
+        <v>1525551655</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>-90</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-648774171</v>
+        <v>-646334854</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>51</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>873650630</v>
+        <v>870365803</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>-20</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2952600777</v>
+        <v>-2941499334</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>39</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>898388636</v>
+        <v>895010797</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>-19</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-955206251</v>
+        <v>-951614785</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>645262970</v>
+        <v>642836854</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>-17</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1792521272</v>
+        <v>-1785781596</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>649252971</v>
+        <v>646811854</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>-14</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2900996763</v>
+        <v>-2890089346</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>635740167</v>
+        <v>633349857</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>280257674</v>
+        <v>279203937</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,391억   ·   현금 40억(1.7%)      오늘 2026-10-20  vs  5일전 2026-10-13      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,403억      오늘 2026-10-20  vs  5일전 2026-10-13      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2075,7 +2075,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1648944000</v>
+        <v>1646445800</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>-150</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-4113450000</v>
+        <v>-4107217999</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>25</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>3187800000</v>
+        <v>3182970386</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>-39</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-2617758000</v>
+        <v>-2613792017</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>21</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2903670000</v>
+        <v>2899270852</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>-30</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-478170000</v>
+        <v>-477445558</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>-25</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-575850000</v>
+        <v>-574977570</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>-20</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-828960000</v>
+        <v>-827704100</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>-6</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1098900000</v>
+        <v>-1097235133</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,004억   ·   현금 46억(2.2%)      오늘 2026-10-20  vs  5일전 2026-10-13      매수 5종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,071억      오늘 2026-10-20  vs  5일전 2026-10-13      매수 5종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2380,7 +2380,7 @@
         <v>145</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>11093255150</v>
+        <v>11093251701</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>-308</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-2990033510</v>
+        <v>-2990032580</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1927587700</v>
+        <v>1927587100</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>-241</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-9460745180</v>
+        <v>-9460742239</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>58</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>961564700</v>
+        <v>961564401</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>-238</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-2191052027</v>
+        <v>-2191051346</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>1026393406</v>
+        <v>1026393087</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>-235</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-2140756222</v>
+        <v>-2140755556</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>8813152913</v>
+        <v>8813150173</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>-125</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-1553650161</v>
+        <v>-1553649678</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>-63</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-1052969509</v>
+        <v>-1052969182</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>-58</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2115666219</v>
+        <v>-2115665562</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>-33</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-4961451514</v>
+        <v>-4961449972</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>-3</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-25939203</v>
+        <v>-25939195</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 276억   ·   현금 3억(1.2%)      오늘 2026-10-20  vs  5일전 2026-10-13      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억      오늘 2026-10-20  vs  5일전 2026-10-13      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2801,11 +2801,11 @@
         <v>17</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>56038817</v>
+        <v>57291666</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.34%→2.54%</t>
+          <t>2.33%→2.54%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2822,11 +2822,11 @@
         <v>-88</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-55481377</v>
+        <v>-62320683</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>7.29%→7.08%</t>
+          <t>7.99%→7.76%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2845,11 +2845,11 @@
         <v>8</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>67964820</v>
+        <v>66088761</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.40%</t>
+          <t>2.05%→2.28%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2866,11 +2866,11 @@
         <v>-31</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-48601815</v>
+        <v>-54521217</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>2.77%→2.59%</t>
+          <t>3.03%→2.83%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2889,11 +2889,11 @@
         <v>6</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>64641619</v>
+        <v>64440562</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>1.31%→1.54%</t>
+          <t>1.27%→1.50%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2910,11 +2910,11 @@
         <v>-8</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-61372018</v>
+        <v>-58959965</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.17%</t>
+          <t>2.25%→2.04%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20261020.xlsx
+++ b/reports/pdf_rolling5_20261020.xlsx
@@ -1451,23 +1451,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-784166884</v>
+        <v>-1948240706</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.11%</t>
+          <t>2.66%→2.38%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1479,23 +1479,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1948240706</v>
+        <v>-784166884</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.38%</t>
+          <t>1.27%→1.11%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261020.xlsx
+++ b/reports/pdf_rolling5_20261020.xlsx
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-463402968</v>
+        <v>-857921711</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.27%</t>
+          <t>5.60%→4.78%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-857921711</v>
+        <v>-1948240706</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>5.60%→4.78%</t>
+          <t>2.66%→2.38%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1451,23 +1451,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1948240706</v>
+        <v>-784166884</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.38%</t>
+          <t>1.27%→1.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1479,23 +1479,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-784166884</v>
+        <v>-463402968</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.11%</t>
+          <t>0.33%→0.27%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261020.xlsx
+++ b/reports/pdf_rolling5_20261020.xlsx
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-857921711</v>
+        <v>-784166884</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>5.60%→4.78%</t>
+          <t>1.27%→1.11%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1948240706</v>
+        <v>-463402968</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.38%</t>
+          <t>0.33%→0.27%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1451,23 +1451,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-784166884</v>
+        <v>-1948240706</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.11%</t>
+          <t>2.66%→2.38%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1479,23 +1479,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-463402968</v>
+        <v>-857921711</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.27%</t>
+          <t>5.60%→4.78%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261020.xlsx
+++ b/reports/pdf_rolling5_20261020.xlsx
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-784166884</v>
+        <v>-857921711</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.11%</t>
+          <t>5.60%→4.78%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>180→173</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-463402968</v>
+        <v>-1948240706</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.27%</t>
+          <t>2.66%→2.38%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>45→38</t>
         </is>
       </c>
     </row>
@@ -1451,23 +1451,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1948240706</v>
+        <v>-784166884</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.38%</t>
+          <t>1.27%→1.11%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>45→38</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1479,23 +1479,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-857921711</v>
+        <v>-463402968</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>5.60%→4.78%</t>
+          <t>0.33%→0.27%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>180→173</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1563,23 +1563,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-958216347</v>
+        <v>-768163478</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.76%</t>
+          <t>7.13%→7.80%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -1591,23 +1591,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-768163478</v>
+        <v>-958216347</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>7.13%→7.80%</t>
+          <t>0.89%→0.76%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
